--- a/erp-server/erp-server-file/src/main/resources/excel/wms/warehouseReceive.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/warehouseReceive.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="仓库收货单" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>收货单号</t>
   </si>
@@ -44,6 +44,12 @@
     <t>作废状态</t>
   </si>
   <si>
+    <t>质检状态</t>
+  </si>
+  <si>
+    <t>入库状态</t>
+  </si>
+  <si>
     <t>SKU</t>
   </si>
   <si>
@@ -56,12 +62,27 @@
     <t>采购数量</t>
   </si>
   <si>
-    <t>超收数量</t>
+    <t>赠品数量</t>
+  </si>
+  <si>
+    <t>入库数量</t>
+  </si>
+  <si>
+    <t>退货数量</t>
+  </si>
+  <si>
+    <t>采购组织</t>
+  </si>
+  <si>
+    <t>收料组织</t>
   </si>
   <si>
     <t>交货仓库</t>
   </si>
   <si>
+    <t>送货单号</t>
+  </si>
+  <si>
     <t>收货日期</t>
   </si>
   <si>
@@ -74,6 +95,9 @@
     <t>审核人</t>
   </si>
   <si>
+    <t>审核完成时间</t>
+  </si>
+  <si>
     <t>收货备注</t>
   </si>
   <si>
@@ -98,6 +122,12 @@
     <t>{.invalidStatusName}</t>
   </si>
   <si>
+    <t>{.qcStatusName}</t>
+  </si>
+  <si>
+    <t>{.inStockStatusName}</t>
+  </si>
+  <si>
     <t>{.skuNo}</t>
   </si>
   <si>
@@ -113,9 +143,24 @@
     <t>{.exceedQty}</t>
   </si>
   <si>
+    <t>{.stockInQty}</t>
+  </si>
+  <si>
+    <t>{.returnQty}</t>
+  </si>
+  <si>
+    <t>{.purchaseOrgName}</t>
+  </si>
+  <si>
+    <t>{.receiveOrgName}</t>
+  </si>
+  <si>
     <t>{.deliveryWarehouseName}</t>
   </si>
   <si>
+    <t>{.deliveryCode}</t>
+  </si>
+  <si>
     <t>{.billDate}</t>
   </si>
   <si>
@@ -126,6 +171,9 @@
   </si>
   <si>
     <t>{.approveUserName}</t>
+  </si>
+  <si>
+    <t>{.approveTime}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -636,7 +684,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1324,13 +1372,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="18" width="30" customWidth="1"/>
+    <col min="1" max="26" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:18">
+    <row r="1" ht="15" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1385,61 +1433,109 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="O2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="P2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>35</v>
+        <v>43</v>
+      </c>
+      <c r="S2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" t="s">
+        <v>46</v>
+      </c>
+      <c r="V2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/warehouseReceive.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/warehouseReceive.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>收货单号</t>
   </si>
@@ -47,6 +47,9 @@
     <t>质检状态</t>
   </si>
   <si>
+    <t>待质检数量</t>
+  </si>
+  <si>
     <t>入库状态</t>
   </si>
   <si>
@@ -123,6 +126,9 @@
   </si>
   <si>
     <t>{.qcStatusName}</t>
+  </si>
+  <si>
+    <t>{.waitQcQty}</t>
   </si>
   <si>
     <t>{.inStockStatusName}</t>
@@ -1372,13 +1378,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="26" width="30" customWidth="1"/>
+    <col min="1" max="27" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:26">
+    <row r="1" ht="15" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1457,85 +1463,91 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Y2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z2" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
